--- a/data/compare_compartment_annotation_with_and_without_manual_curation.xlsx
+++ b/data/compare_compartment_annotation_with_and_without_manual_curation.xlsx
@@ -618,7 +618,7 @@
         <v>546</v>
       </c>
       <c r="D12" t="n">
-        <v>268</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13">

--- a/data/compare_compartment_annotation_with_and_without_manual_curation.xlsx
+++ b/data/compare_compartment_annotation_with_and_without_manual_curation.xlsx
@@ -458,7 +458,7 @@
         <v>1126</v>
       </c>
       <c r="D2" t="n">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +506,7 @@
         <v>788</v>
       </c>
       <c r="D5" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6">
@@ -762,7 +762,7 @@
         <v>464</v>
       </c>
       <c r="D21" t="n">
-        <v>359</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22">
@@ -1674,7 +1674,7 @@
         <v>239</v>
       </c>
       <c r="D78" t="n">
-        <v>239</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79">
